--- a/datos/indicadores_adelantados/transporte/indice_general_transporte_2017_2026.xlsx
+++ b/datos/indicadores_adelantados/transporte/indice_general_transporte_2017_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\clopez\Documents\TRANSPORTE\TRANS AGQ\Cuadros de salida Transporte\Pagina web\Indicadores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CAB1CB5-1A3A-402F-930A-3CF8B71B94AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{178DC5CF-A493-43BB-A5CB-1E2466E760F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="743" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,14 +23,14 @@
     <sheet name="Ponderadores" sheetId="14" state="hidden" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Indice!$B$2:$H$142</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Indice!$B$2:$H$143</definedName>
   </definedNames>
   <calcPr calcId="181029" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="811" uniqueCount="59">
   <si>
     <t>PERIODO</t>
   </si>
@@ -20184,7 +20184,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:L150"/>
+  <dimension ref="B1:L151"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="1.7109375" style="1" customWidth="1"/>
@@ -23168,22 +23168,22 @@
         <v>53</v>
       </c>
       <c r="C133" s="51">
-        <v>87.092207734861205</v>
+        <v>93.364234170342499</v>
       </c>
       <c r="D133" s="51">
-        <v>79.801372783783194</v>
+        <v>79.604501405984493</v>
       </c>
       <c r="E133" s="51">
-        <v>117.755787042004</v>
+        <v>120.235209249821</v>
       </c>
       <c r="F133" s="51">
-        <v>89.691648433231606</v>
+        <v>90.370010267431596</v>
       </c>
       <c r="G133" s="51">
-        <v>82.978882508627294</v>
+        <v>85.022565005083493</v>
       </c>
       <c r="H133" s="51">
-        <v>85.567674730133405</v>
+        <v>86.741796362828694</v>
       </c>
     </row>
     <row r="134" spans="2:8" x14ac:dyDescent="0.2">
@@ -23324,38 +23324,53 @@
         <v>62.3156566035194</v>
       </c>
     </row>
-    <row r="140" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B140" s="48"/>
-      <c r="C140" s="53"/>
-      <c r="D140" s="53"/>
-      <c r="E140" s="53"/>
-      <c r="F140" s="49"/>
-      <c r="G140" s="53"/>
-      <c r="H140" s="49"/>
-    </row>
-    <row r="141" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B141" s="55" t="s">
+    <row r="140" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B140" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="C140" s="53">
+        <v>130.99639278322999</v>
+      </c>
+      <c r="D140" s="53">
+        <v>78.423273139192304</v>
+      </c>
+      <c r="E140" s="53">
+        <v>135.11174249672001</v>
+      </c>
+      <c r="F140" s="49">
+        <v>94.440181272631193</v>
+      </c>
+      <c r="G140" s="53">
+        <v>97.284659983820603</v>
+      </c>
+      <c r="H140" s="49">
+        <v>93.786526159000601</v>
+      </c>
+    </row>
+    <row r="141" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B141" s="48"/>
+      <c r="C141" s="53"/>
+      <c r="D141" s="53"/>
+      <c r="E141" s="53"/>
+      <c r="F141" s="49"/>
+      <c r="G141" s="53"/>
+      <c r="H141" s="49"/>
+    </row>
+    <row r="142" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B142" s="55" t="s">
         <v>52</v>
       </c>
-      <c r="C141" s="43"/>
-      <c r="D141" s="43"/>
-      <c r="E141" s="44"/>
-      <c r="F141" s="43"/>
-      <c r="G141" s="43"/>
-      <c r="H141" s="44"/>
-    </row>
-    <row r="142" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B142" s="56" t="s">
+      <c r="C142" s="43"/>
+      <c r="D142" s="43"/>
+      <c r="E142" s="44"/>
+      <c r="F142" s="43"/>
+      <c r="G142" s="43"/>
+      <c r="H142" s="44"/>
+    </row>
+    <row r="143" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B143" s="56" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="143" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C143" s="65"/>
-      <c r="D143" s="65"/>
-      <c r="E143" s="65"/>
-      <c r="F143" s="65"/>
-      <c r="G143" s="65"/>
-      <c r="H143" s="65"/>
     </row>
     <row r="144" spans="2:8" x14ac:dyDescent="0.2">
       <c r="C144" s="65"/>
@@ -23382,12 +23397,12 @@
       <c r="H146" s="65"/>
     </row>
     <row r="147" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C147" s="68"/>
-      <c r="D147" s="68"/>
-      <c r="E147" s="68"/>
-      <c r="F147" s="68"/>
-      <c r="G147" s="68"/>
-      <c r="H147" s="68"/>
+      <c r="C147" s="65"/>
+      <c r="D147" s="65"/>
+      <c r="E147" s="65"/>
+      <c r="F147" s="65"/>
+      <c r="G147" s="65"/>
+      <c r="H147" s="65"/>
     </row>
     <row r="148" spans="3:8" x14ac:dyDescent="0.2">
       <c r="C148" s="68"/>
@@ -23412,6 +23427,14 @@
       <c r="F150" s="68"/>
       <c r="G150" s="68"/>
       <c r="H150" s="68"/>
+    </row>
+    <row r="151" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C151" s="68"/>
+      <c r="D151" s="68"/>
+      <c r="E151" s="68"/>
+      <c r="F151" s="68"/>
+      <c r="G151" s="68"/>
+      <c r="H151" s="68"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -23435,7 +23458,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B1:I138"/>
+  <dimension ref="B1:I139"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="1.7109375" style="13" customWidth="1"/>
@@ -26192,22 +26215,22 @@
         <v>53</v>
       </c>
       <c r="C119" s="51">
-        <v>5.9041371390831001</v>
+        <v>5.0382294651177197</v>
       </c>
       <c r="D119" s="51">
-        <v>-6.9516321918771196</v>
+        <v>-10.4646373190066</v>
       </c>
       <c r="E119" s="51">
-        <v>-9.4848465871623908</v>
+        <v>-8.5019914466273594</v>
       </c>
       <c r="F119" s="51">
-        <v>2.1739821659236598</v>
+        <v>1.44596380048073</v>
       </c>
       <c r="G119" s="51">
-        <v>1.6963779084239701</v>
+        <v>2.1250581927347798</v>
       </c>
       <c r="H119" s="51">
-        <v>-3.2203843073128402</v>
+        <v>-4.3387648809647201</v>
       </c>
       <c r="I119" s="61"/>
     </row>
@@ -26355,47 +26378,63 @@
       </c>
       <c r="I125" s="61"/>
     </row>
-    <row r="126" spans="2:9" s="1" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B126" s="48"/>
-      <c r="C126" s="49"/>
-      <c r="D126" s="49"/>
-      <c r="E126" s="49"/>
-      <c r="F126" s="49"/>
-      <c r="G126" s="49"/>
-      <c r="H126" s="49"/>
+    <row r="126" spans="2:9" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B126" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="C126" s="49">
+        <v>1.7205192921860799</v>
+      </c>
+      <c r="D126" s="49">
+        <v>-27.237094917050701</v>
+      </c>
+      <c r="E126" s="49">
+        <v>-2.9938120694372299</v>
+      </c>
+      <c r="F126" s="49">
+        <v>-2.5122435002904799</v>
+      </c>
+      <c r="G126" s="49">
+        <v>4.3767357680816596</v>
+      </c>
+      <c r="H126" s="49">
+        <v>-10.0302150124951</v>
+      </c>
       <c r="I126" s="61"/>
     </row>
-    <row r="127" spans="2:9" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="B127" s="63" t="s">
+    <row r="127" spans="2:9" s="1" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B127" s="48"/>
+      <c r="C127" s="49"/>
+      <c r="D127" s="49"/>
+      <c r="E127" s="49"/>
+      <c r="F127" s="49"/>
+      <c r="G127" s="49"/>
+      <c r="H127" s="49"/>
+      <c r="I127" s="61"/>
+    </row>
+    <row r="128" spans="2:9" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="B128" s="63" t="s">
         <v>52</v>
       </c>
-      <c r="C127" s="45"/>
-      <c r="D127" s="45"/>
-      <c r="E127" s="45"/>
-      <c r="F127" s="45"/>
-      <c r="G127" s="45"/>
-      <c r="H127" s="45"/>
-    </row>
-    <row r="128" spans="2:9" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="B128" s="64" t="s">
+      <c r="C128" s="45"/>
+      <c r="D128" s="45"/>
+      <c r="E128" s="45"/>
+      <c r="F128" s="45"/>
+      <c r="G128" s="45"/>
+      <c r="H128" s="45"/>
+    </row>
+    <row r="129" spans="2:8" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="B129" s="64" t="s">
         <v>21</v>
       </c>
-      <c r="C128" s="34"/>
-      <c r="D128" s="34"/>
-      <c r="E128" s="34"/>
-      <c r="F128" s="34"/>
-      <c r="G128" s="34"/>
-      <c r="H128" s="34"/>
-    </row>
-    <row r="130" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C130" s="66"/>
-      <c r="D130" s="66"/>
-      <c r="E130" s="66"/>
-      <c r="F130" s="66"/>
-      <c r="G130" s="66"/>
-      <c r="H130" s="67"/>
-    </row>
-    <row r="131" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C129" s="34"/>
+      <c r="D129" s="34"/>
+      <c r="E129" s="34"/>
+      <c r="F129" s="34"/>
+      <c r="G129" s="34"/>
+      <c r="H129" s="34"/>
+    </row>
+    <row r="131" spans="2:8" x14ac:dyDescent="0.2">
       <c r="C131" s="66"/>
       <c r="D131" s="66"/>
       <c r="E131" s="66"/>
@@ -26403,7 +26442,7 @@
       <c r="G131" s="66"/>
       <c r="H131" s="67"/>
     </row>
-    <row r="132" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="132" spans="2:8" x14ac:dyDescent="0.2">
       <c r="C132" s="66"/>
       <c r="D132" s="66"/>
       <c r="E132" s="66"/>
@@ -26411,7 +26450,7 @@
       <c r="G132" s="66"/>
       <c r="H132" s="67"/>
     </row>
-    <row r="133" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="133" spans="2:8" x14ac:dyDescent="0.2">
       <c r="C133" s="66"/>
       <c r="D133" s="66"/>
       <c r="E133" s="66"/>
@@ -26419,15 +26458,15 @@
       <c r="G133" s="66"/>
       <c r="H133" s="67"/>
     </row>
-    <row r="135" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C135" s="69"/>
-      <c r="D135" s="69"/>
-      <c r="E135" s="69"/>
-      <c r="F135" s="69"/>
-      <c r="G135" s="69"/>
-      <c r="H135" s="69"/>
-    </row>
-    <row r="136" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="134" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="C134" s="66"/>
+      <c r="D134" s="66"/>
+      <c r="E134" s="66"/>
+      <c r="F134" s="66"/>
+      <c r="G134" s="66"/>
+      <c r="H134" s="67"/>
+    </row>
+    <row r="136" spans="2:8" x14ac:dyDescent="0.2">
       <c r="C136" s="69"/>
       <c r="D136" s="69"/>
       <c r="E136" s="69"/>
@@ -26435,7 +26474,7 @@
       <c r="G136" s="69"/>
       <c r="H136" s="69"/>
     </row>
-    <row r="137" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="137" spans="2:8" x14ac:dyDescent="0.2">
       <c r="C137" s="69"/>
       <c r="D137" s="69"/>
       <c r="E137" s="69"/>
@@ -26443,13 +26482,21 @@
       <c r="G137" s="69"/>
       <c r="H137" s="69"/>
     </row>
-    <row r="138" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="138" spans="2:8" x14ac:dyDescent="0.2">
       <c r="C138" s="69"/>
       <c r="D138" s="69"/>
       <c r="E138" s="69"/>
       <c r="F138" s="69"/>
       <c r="G138" s="69"/>
       <c r="H138" s="69"/>
+    </row>
+    <row r="139" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="C139" s="69"/>
+      <c r="D139" s="69"/>
+      <c r="E139" s="69"/>
+      <c r="F139" s="69"/>
+      <c r="G139" s="69"/>
+      <c r="H139" s="69"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -26473,7 +26520,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="B1:I136"/>
+  <dimension ref="B1:I137"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="1.7109375" style="13" customWidth="1"/>
@@ -29230,22 +29277,22 @@
         <v>53</v>
       </c>
       <c r="C119" s="51">
-        <v>5.9041371390831001</v>
+        <v>5.0382294651177197</v>
       </c>
       <c r="D119" s="51">
-        <v>-6.9516321918771196</v>
+        <v>-10.4646373190066</v>
       </c>
       <c r="E119" s="51">
-        <v>-9.4848465871623908</v>
+        <v>-8.5019914466273594</v>
       </c>
       <c r="F119" s="51">
-        <v>2.1739821659236598</v>
+        <v>1.44596380048073</v>
       </c>
       <c r="G119" s="51">
-        <v>1.6963779084239701</v>
+        <v>2.1250581927347798</v>
       </c>
       <c r="H119" s="51">
-        <v>-3.2203843073128402</v>
+        <v>-4.3387648809647201</v>
       </c>
       <c r="I119" s="61"/>
     </row>
@@ -29393,47 +29440,63 @@
       </c>
       <c r="I125" s="61"/>
     </row>
-    <row r="126" spans="2:9" s="1" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B126" s="48"/>
-      <c r="C126" s="49"/>
-      <c r="D126" s="49"/>
-      <c r="E126" s="49"/>
-      <c r="F126" s="49"/>
-      <c r="G126" s="49"/>
-      <c r="H126" s="49"/>
+    <row r="126" spans="2:9" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B126" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="C126" s="49">
+        <v>38.891808708261003</v>
+      </c>
+      <c r="D126" s="49">
+        <v>131.918165039294</v>
+      </c>
+      <c r="E126" s="49">
+        <v>13.079044668357501</v>
+      </c>
+      <c r="F126" s="49">
+        <v>5.4425520699895298</v>
+      </c>
+      <c r="G126" s="49">
+        <v>36.5711786256675</v>
+      </c>
+      <c r="H126" s="49">
+        <v>50.502347677587998</v>
+      </c>
       <c r="I126" s="61"/>
     </row>
-    <row r="127" spans="2:9" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="B127" s="63" t="s">
+    <row r="127" spans="2:9" s="1" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B127" s="48"/>
+      <c r="C127" s="49"/>
+      <c r="D127" s="49"/>
+      <c r="E127" s="49"/>
+      <c r="F127" s="49"/>
+      <c r="G127" s="49"/>
+      <c r="H127" s="49"/>
+      <c r="I127" s="61"/>
+    </row>
+    <row r="128" spans="2:9" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="B128" s="63" t="s">
         <v>52</v>
       </c>
-      <c r="C127" s="45"/>
-      <c r="D127" s="45"/>
-      <c r="E127" s="45"/>
-      <c r="F127" s="45"/>
-      <c r="G127" s="45"/>
-      <c r="H127" s="45"/>
-    </row>
-    <row r="128" spans="2:9" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="B128" s="64" t="s">
+      <c r="C128" s="45"/>
+      <c r="D128" s="45"/>
+      <c r="E128" s="45"/>
+      <c r="F128" s="45"/>
+      <c r="G128" s="45"/>
+      <c r="H128" s="45"/>
+    </row>
+    <row r="129" spans="2:8" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="B129" s="64" t="s">
         <v>21</v>
       </c>
-      <c r="C128" s="34"/>
-      <c r="D128" s="34"/>
-      <c r="E128" s="34"/>
-      <c r="F128" s="34"/>
-      <c r="G128" s="34"/>
-      <c r="H128" s="34"/>
-    </row>
-    <row r="130" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C130" s="66"/>
-      <c r="D130" s="66"/>
-      <c r="E130" s="66"/>
-      <c r="F130" s="66"/>
-      <c r="G130" s="66"/>
-      <c r="H130" s="67"/>
-    </row>
-    <row r="131" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C129" s="34"/>
+      <c r="D129" s="34"/>
+      <c r="E129" s="34"/>
+      <c r="F129" s="34"/>
+      <c r="G129" s="34"/>
+      <c r="H129" s="34"/>
+    </row>
+    <row r="131" spans="2:8" x14ac:dyDescent="0.2">
       <c r="C131" s="66"/>
       <c r="D131" s="66"/>
       <c r="E131" s="66"/>
@@ -29441,7 +29504,7 @@
       <c r="G131" s="66"/>
       <c r="H131" s="67"/>
     </row>
-    <row r="132" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="132" spans="2:8" x14ac:dyDescent="0.2">
       <c r="C132" s="66"/>
       <c r="D132" s="66"/>
       <c r="E132" s="66"/>
@@ -29449,15 +29512,15 @@
       <c r="G132" s="66"/>
       <c r="H132" s="67"/>
     </row>
-    <row r="133" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="133" spans="2:8" x14ac:dyDescent="0.2">
       <c r="C133" s="66"/>
       <c r="D133" s="66"/>
       <c r="E133" s="66"/>
       <c r="F133" s="66"/>
       <c r="G133" s="66"/>
-      <c r="H133" s="66"/>
-    </row>
-    <row r="134" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="H133" s="67"/>
+    </row>
+    <row r="134" spans="2:8" x14ac:dyDescent="0.2">
       <c r="C134" s="66"/>
       <c r="D134" s="66"/>
       <c r="E134" s="66"/>
@@ -29465,7 +29528,7 @@
       <c r="G134" s="66"/>
       <c r="H134" s="66"/>
     </row>
-    <row r="135" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="135" spans="2:8" x14ac:dyDescent="0.2">
       <c r="C135" s="66"/>
       <c r="D135" s="66"/>
       <c r="E135" s="66"/>
@@ -29473,13 +29536,21 @@
       <c r="G135" s="66"/>
       <c r="H135" s="66"/>
     </row>
-    <row r="136" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="136" spans="2:8" x14ac:dyDescent="0.2">
       <c r="C136" s="66"/>
       <c r="D136" s="66"/>
       <c r="E136" s="66"/>
       <c r="F136" s="66"/>
       <c r="G136" s="66"/>
       <c r="H136" s="66"/>
+    </row>
+    <row r="137" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="C137" s="66"/>
+      <c r="D137" s="66"/>
+      <c r="E137" s="66"/>
+      <c r="F137" s="66"/>
+      <c r="G137" s="66"/>
+      <c r="H137" s="66"/>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/datos/indicadores_adelantados/transporte/indice_general_transporte_2017_2026.xlsx
+++ b/datos/indicadores_adelantados/transporte/indice_general_transporte_2017_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\clopez\Documents\TRANSPORTE\TRANS AGQ\Cuadros de salida Transporte\Pagina web\Indicadores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{178DC5CF-A493-43BB-A5CB-1E2466E760F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAFA6AC8-49CE-42A0-8AB4-ACE0E9440EC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="743" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,14 +23,14 @@
     <sheet name="Ponderadores" sheetId="14" state="hidden" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Indice!$B$2:$H$143</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Indice!$B$2:$H$144</definedName>
   </definedNames>
   <calcPr calcId="181029" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="811" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="59">
   <si>
     <t>PERIODO</t>
   </si>
@@ -20184,7 +20184,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:L151"/>
+  <dimension ref="B1:L152"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="1.7109375" style="1" customWidth="1"/>
@@ -23168,22 +23168,22 @@
         <v>53</v>
       </c>
       <c r="C133" s="51">
-        <v>93.364234170342499</v>
+        <v>96.170244831518204</v>
       </c>
       <c r="D133" s="51">
-        <v>79.604501405984493</v>
+        <v>82.230665631638402</v>
       </c>
       <c r="E133" s="51">
-        <v>120.235209249821</v>
+        <v>121.12371214441301</v>
       </c>
       <c r="F133" s="51">
-        <v>90.370010267431596</v>
+        <v>90.726776675699099</v>
       </c>
       <c r="G133" s="51">
-        <v>85.022565005083493</v>
+        <v>86.083998580326806</v>
       </c>
       <c r="H133" s="51">
-        <v>86.741796362828694</v>
+        <v>88.396439549356998</v>
       </c>
     </row>
     <row r="134" spans="2:8" x14ac:dyDescent="0.2">
@@ -23347,38 +23347,53 @@
         <v>93.786526159000601</v>
       </c>
     </row>
-    <row r="141" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B141" s="48"/>
-      <c r="C141" s="53"/>
-      <c r="D141" s="53"/>
-      <c r="E141" s="53"/>
-      <c r="F141" s="49"/>
-      <c r="G141" s="53"/>
-      <c r="H141" s="49"/>
-    </row>
-    <row r="142" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B142" s="55" t="s">
+    <row r="141" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B141" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="C141" s="53">
+        <v>115.812319459748</v>
+      </c>
+      <c r="D141" s="53">
+        <v>100.61381521121599</v>
+      </c>
+      <c r="E141" s="53">
+        <v>127.343232406555</v>
+      </c>
+      <c r="F141" s="49">
+        <v>93.224141533571895</v>
+      </c>
+      <c r="G141" s="53">
+        <v>93.514033607030299</v>
+      </c>
+      <c r="H141" s="49">
+        <v>99.978941855054998</v>
+      </c>
+    </row>
+    <row r="142" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B142" s="48"/>
+      <c r="C142" s="53"/>
+      <c r="D142" s="53"/>
+      <c r="E142" s="53"/>
+      <c r="F142" s="49"/>
+      <c r="G142" s="53"/>
+      <c r="H142" s="49"/>
+    </row>
+    <row r="143" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B143" s="55" t="s">
         <v>52</v>
       </c>
-      <c r="C142" s="43"/>
-      <c r="D142" s="43"/>
-      <c r="E142" s="44"/>
-      <c r="F142" s="43"/>
-      <c r="G142" s="43"/>
-      <c r="H142" s="44"/>
-    </row>
-    <row r="143" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B143" s="56" t="s">
+      <c r="C143" s="43"/>
+      <c r="D143" s="43"/>
+      <c r="E143" s="44"/>
+      <c r="F143" s="43"/>
+      <c r="G143" s="43"/>
+      <c r="H143" s="44"/>
+    </row>
+    <row r="144" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B144" s="56" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="144" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C144" s="65"/>
-      <c r="D144" s="65"/>
-      <c r="E144" s="65"/>
-      <c r="F144" s="65"/>
-      <c r="G144" s="65"/>
-      <c r="H144" s="65"/>
     </row>
     <row r="145" spans="3:8" x14ac:dyDescent="0.2">
       <c r="C145" s="65"/>
@@ -23405,12 +23420,12 @@
       <c r="H147" s="65"/>
     </row>
     <row r="148" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C148" s="68"/>
-      <c r="D148" s="68"/>
-      <c r="E148" s="68"/>
-      <c r="F148" s="68"/>
-      <c r="G148" s="68"/>
-      <c r="H148" s="68"/>
+      <c r="C148" s="65"/>
+      <c r="D148" s="65"/>
+      <c r="E148" s="65"/>
+      <c r="F148" s="65"/>
+      <c r="G148" s="65"/>
+      <c r="H148" s="65"/>
     </row>
     <row r="149" spans="3:8" x14ac:dyDescent="0.2">
       <c r="C149" s="68"/>
@@ -23435,6 +23450,14 @@
       <c r="F151" s="68"/>
       <c r="G151" s="68"/>
       <c r="H151" s="68"/>
+    </row>
+    <row r="152" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C152" s="68"/>
+      <c r="D152" s="68"/>
+      <c r="E152" s="68"/>
+      <c r="F152" s="68"/>
+      <c r="G152" s="68"/>
+      <c r="H152" s="68"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -23458,7 +23481,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B1:I139"/>
+  <dimension ref="B1:I140"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="1.7109375" style="13" customWidth="1"/>
@@ -26215,22 +26238,22 @@
         <v>53</v>
       </c>
       <c r="C119" s="51">
-        <v>5.0382294651177197</v>
+        <v>6.1879286348850302</v>
       </c>
       <c r="D119" s="51">
-        <v>-10.4646373190066</v>
+        <v>-8.9129427864952504</v>
       </c>
       <c r="E119" s="51">
-        <v>-8.5019914466273594</v>
+        <v>-7.0062236906078503</v>
       </c>
       <c r="F119" s="51">
-        <v>1.44596380048073</v>
+        <v>1.0965468292115199</v>
       </c>
       <c r="G119" s="51">
-        <v>2.1250581927347798</v>
+        <v>2.12925506861981</v>
       </c>
       <c r="H119" s="51">
-        <v>-4.3387648809647201</v>
+        <v>-3.51314704590173</v>
       </c>
       <c r="I119" s="61"/>
     </row>
@@ -26402,45 +26425,61 @@
       </c>
       <c r="I126" s="61"/>
     </row>
-    <row r="127" spans="2:9" s="1" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B127" s="48"/>
-      <c r="C127" s="49"/>
-      <c r="D127" s="49"/>
-      <c r="E127" s="49"/>
-      <c r="F127" s="49"/>
-      <c r="G127" s="49"/>
-      <c r="H127" s="49"/>
+    <row r="127" spans="2:9" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B127" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="C127" s="49">
+        <v>13.178704242044599</v>
+      </c>
+      <c r="D127" s="49">
+        <v>0.75801000472128499</v>
+      </c>
+      <c r="E127" s="49">
+        <v>4.2584211358072404</v>
+      </c>
+      <c r="F127" s="49">
+        <v>-1.21235690042424</v>
+      </c>
+      <c r="G127" s="49">
+        <v>2.1559736274446801</v>
+      </c>
+      <c r="H127" s="49">
+        <v>1.8240257205183199</v>
+      </c>
       <c r="I127" s="61"/>
     </row>
-    <row r="128" spans="2:9" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="B128" s="63" t="s">
+    <row r="128" spans="2:9" s="1" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B128" s="48"/>
+      <c r="C128" s="49"/>
+      <c r="D128" s="49"/>
+      <c r="E128" s="49"/>
+      <c r="F128" s="49"/>
+      <c r="G128" s="49"/>
+      <c r="H128" s="49"/>
+      <c r="I128" s="61"/>
+    </row>
+    <row r="129" spans="2:8" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="B129" s="63" t="s">
         <v>52</v>
       </c>
-      <c r="C128" s="45"/>
-      <c r="D128" s="45"/>
-      <c r="E128" s="45"/>
-      <c r="F128" s="45"/>
-      <c r="G128" s="45"/>
-      <c r="H128" s="45"/>
-    </row>
-    <row r="129" spans="2:8" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="B129" s="64" t="s">
+      <c r="C129" s="45"/>
+      <c r="D129" s="45"/>
+      <c r="E129" s="45"/>
+      <c r="F129" s="45"/>
+      <c r="G129" s="45"/>
+      <c r="H129" s="45"/>
+    </row>
+    <row r="130" spans="2:8" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="B130" s="64" t="s">
         <v>21</v>
       </c>
-      <c r="C129" s="34"/>
-      <c r="D129" s="34"/>
-      <c r="E129" s="34"/>
-      <c r="F129" s="34"/>
-      <c r="G129" s="34"/>
-      <c r="H129" s="34"/>
-    </row>
-    <row r="131" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C131" s="66"/>
-      <c r="D131" s="66"/>
-      <c r="E131" s="66"/>
-      <c r="F131" s="66"/>
-      <c r="G131" s="66"/>
-      <c r="H131" s="67"/>
+      <c r="C130" s="34"/>
+      <c r="D130" s="34"/>
+      <c r="E130" s="34"/>
+      <c r="F130" s="34"/>
+      <c r="G130" s="34"/>
+      <c r="H130" s="34"/>
     </row>
     <row r="132" spans="2:8" x14ac:dyDescent="0.2">
       <c r="C132" s="66"/>
@@ -26466,13 +26505,13 @@
       <c r="G134" s="66"/>
       <c r="H134" s="67"/>
     </row>
-    <row r="136" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C136" s="69"/>
-      <c r="D136" s="69"/>
-      <c r="E136" s="69"/>
-      <c r="F136" s="69"/>
-      <c r="G136" s="69"/>
-      <c r="H136" s="69"/>
+    <row r="135" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="C135" s="66"/>
+      <c r="D135" s="66"/>
+      <c r="E135" s="66"/>
+      <c r="F135" s="66"/>
+      <c r="G135" s="66"/>
+      <c r="H135" s="67"/>
     </row>
     <row r="137" spans="2:8" x14ac:dyDescent="0.2">
       <c r="C137" s="69"/>
@@ -26497,6 +26536,14 @@
       <c r="F139" s="69"/>
       <c r="G139" s="69"/>
       <c r="H139" s="69"/>
+    </row>
+    <row r="140" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="C140" s="69"/>
+      <c r="D140" s="69"/>
+      <c r="E140" s="69"/>
+      <c r="F140" s="69"/>
+      <c r="G140" s="69"/>
+      <c r="H140" s="69"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -26520,7 +26567,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="B1:I137"/>
+  <dimension ref="B1:I138"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="1.7109375" style="13" customWidth="1"/>
@@ -29277,22 +29324,22 @@
         <v>53</v>
       </c>
       <c r="C119" s="51">
-        <v>5.0382294651177197</v>
+        <v>6.1879286348850302</v>
       </c>
       <c r="D119" s="51">
-        <v>-10.4646373190066</v>
+        <v>-8.9129427864952504</v>
       </c>
       <c r="E119" s="51">
-        <v>-8.5019914466273594</v>
+        <v>-7.0062236906078503</v>
       </c>
       <c r="F119" s="51">
-        <v>1.44596380048073</v>
+        <v>1.0965468292115199</v>
       </c>
       <c r="G119" s="51">
-        <v>2.1250581927347798</v>
+        <v>2.12925506861981</v>
       </c>
       <c r="H119" s="51">
-        <v>-4.3387648809647201</v>
+        <v>-3.51314704590173</v>
       </c>
       <c r="I119" s="61"/>
     </row>
@@ -29464,45 +29511,61 @@
       </c>
       <c r="I126" s="61"/>
     </row>
-    <row r="127" spans="2:9" s="1" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B127" s="48"/>
-      <c r="C127" s="49"/>
-      <c r="D127" s="49"/>
-      <c r="E127" s="49"/>
-      <c r="F127" s="49"/>
-      <c r="G127" s="49"/>
-      <c r="H127" s="49"/>
+    <row r="127" spans="2:9" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B127" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="C127" s="49">
+        <v>-11.5912148425402</v>
+      </c>
+      <c r="D127" s="49">
+        <v>28.2958631841826</v>
+      </c>
+      <c r="E127" s="49">
+        <v>-5.7496927703035103</v>
+      </c>
+      <c r="F127" s="49">
+        <v>-1.2876296113291199</v>
+      </c>
+      <c r="G127" s="49">
+        <v>-3.8758694098508402</v>
+      </c>
+      <c r="H127" s="49">
+        <v>6.6026709269048904</v>
+      </c>
       <c r="I127" s="61"/>
     </row>
-    <row r="128" spans="2:9" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="B128" s="63" t="s">
+    <row r="128" spans="2:9" s="1" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B128" s="48"/>
+      <c r="C128" s="49"/>
+      <c r="D128" s="49"/>
+      <c r="E128" s="49"/>
+      <c r="F128" s="49"/>
+      <c r="G128" s="49"/>
+      <c r="H128" s="49"/>
+      <c r="I128" s="61"/>
+    </row>
+    <row r="129" spans="2:8" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="B129" s="63" t="s">
         <v>52</v>
       </c>
-      <c r="C128" s="45"/>
-      <c r="D128" s="45"/>
-      <c r="E128" s="45"/>
-      <c r="F128" s="45"/>
-      <c r="G128" s="45"/>
-      <c r="H128" s="45"/>
-    </row>
-    <row r="129" spans="2:8" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="B129" s="64" t="s">
+      <c r="C129" s="45"/>
+      <c r="D129" s="45"/>
+      <c r="E129" s="45"/>
+      <c r="F129" s="45"/>
+      <c r="G129" s="45"/>
+      <c r="H129" s="45"/>
+    </row>
+    <row r="130" spans="2:8" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="B130" s="64" t="s">
         <v>21</v>
       </c>
-      <c r="C129" s="34"/>
-      <c r="D129" s="34"/>
-      <c r="E129" s="34"/>
-      <c r="F129" s="34"/>
-      <c r="G129" s="34"/>
-      <c r="H129" s="34"/>
-    </row>
-    <row r="131" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C131" s="66"/>
-      <c r="D131" s="66"/>
-      <c r="E131" s="66"/>
-      <c r="F131" s="66"/>
-      <c r="G131" s="66"/>
-      <c r="H131" s="67"/>
+      <c r="C130" s="34"/>
+      <c r="D130" s="34"/>
+      <c r="E130" s="34"/>
+      <c r="F130" s="34"/>
+      <c r="G130" s="34"/>
+      <c r="H130" s="34"/>
     </row>
     <row r="132" spans="2:8" x14ac:dyDescent="0.2">
       <c r="C132" s="66"/>
@@ -29526,7 +29589,7 @@
       <c r="E134" s="66"/>
       <c r="F134" s="66"/>
       <c r="G134" s="66"/>
-      <c r="H134" s="66"/>
+      <c r="H134" s="67"/>
     </row>
     <row r="135" spans="2:8" x14ac:dyDescent="0.2">
       <c r="C135" s="66"/>
@@ -29551,6 +29614,14 @@
       <c r="F137" s="66"/>
       <c r="G137" s="66"/>
       <c r="H137" s="66"/>
+    </row>
+    <row r="138" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="C138" s="66"/>
+      <c r="D138" s="66"/>
+      <c r="E138" s="66"/>
+      <c r="F138" s="66"/>
+      <c r="G138" s="66"/>
+      <c r="H138" s="66"/>
     </row>
   </sheetData>
   <mergeCells count="8">
